--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -1078,7 +1078,7 @@
     <t>0.0005,0.9644,0.7845,0.0005</t>
   </si>
   <si>
-    <t>0.0002,0.8717,0.9892,0.0001</t>
+    <t>0.0002,0.8718,0.9892,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9930,0.9758,0.0000</t>
@@ -1174,7 +1174,7 @@
     <t>0.5540,0.0077,0.4544,0.0012</t>
   </si>
   <si>
-    <t>0.2553,0.0117,0.7675,0.0053</t>
+    <t>0.2552,0.0117,0.7675,0.0053</t>
   </si>
   <si>
     <t>0.0009,0.7696,0.7781,0.1131</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="527">
   <si>
     <t>Filename</t>
   </si>
@@ -814,31 +814,40 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
     <t>0,1,0,1</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0.9737,0.0030,0.0067,0.0007</t>
   </si>
   <si>
-    <t>0.0179,0.0035,0.0001,0.9940</t>
-  </si>
-  <si>
-    <t>0.9270,0.0022,0.0003,0.0233</t>
-  </si>
-  <si>
-    <t>0.4508,0.0010,0.0009,0.4889</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0010,0.0004</t>
+    <t>0.0178,0.0035,0.0001,0.9941</t>
+  </si>
+  <si>
+    <t>0.9266,0.0022,0.0003,0.0235</t>
+  </si>
+  <si>
+    <t>0.4491,0.0010,0.0009,0.4915</t>
+  </si>
+  <si>
+    <t>0.9928,0.0022,0.0010,0.0004</t>
   </si>
   <si>
     <t>0.9910,0.0060,0.0006,0.0004</t>
@@ -865,16 +874,16 @@
     <t>0.8476,0.0081,0.1277,0.0013</t>
   </si>
   <si>
-    <t>0.0232,0.0605,0.9369,0.0026</t>
-  </si>
-  <si>
-    <t>0.1578,0.0010,0.8983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0801,0.0048,0.9349,0.0011</t>
-  </si>
-  <si>
-    <t>0.5843,0.0016,0.4812,0.0004</t>
+    <t>0.0232,0.0607,0.9367,0.0026</t>
+  </si>
+  <si>
+    <t>0.1580,0.0010,0.8982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0802,0.0048,0.9349,0.0011</t>
+  </si>
+  <si>
+    <t>0.5845,0.0016,0.4809,0.0004</t>
   </si>
   <si>
     <t>0.0011,0.9988,0.0061,0.0002</t>
@@ -883,19 +892,19 @@
     <t>0.0021,0.9968,0.0032,0.0012</t>
   </si>
   <si>
-    <t>0.2115,0.9181,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.9945,0.0075,0.0030</t>
+    <t>0.2115,0.9180,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9946,0.0075,0.0030</t>
   </si>
   <si>
     <t>0.0014,0.9991,0.0260,0.0000</t>
   </si>
   <si>
-    <t>0.5700,0.0006,0.5346,0.0005</t>
-  </si>
-  <si>
-    <t>0.0935,0.0085,0.9138,0.0048</t>
+    <t>0.5700,0.0006,0.5345,0.0005</t>
+  </si>
+  <si>
+    <t>0.0937,0.0085,0.9136,0.0048</t>
   </si>
   <si>
     <t>0.0217,0.0002,0.9899,0.0001</t>
@@ -913,7 +922,7 @@
     <t>0.0109,0.0005,0.9924,0.0003</t>
   </si>
   <si>
-    <t>0.6806,0.3744,0.0309,0.0010</t>
+    <t>0.6799,0.3753,0.0309,0.0011</t>
   </si>
   <si>
     <t>0.9556,0.0511,0.0040,0.0007</t>
@@ -922,43 +931,43 @@
     <t>0.0016,0.0001,0.9985,0.0002</t>
   </si>
   <si>
-    <t>0.0208,0.3170,0.8351,0.0016</t>
+    <t>0.0208,0.3181,0.8348,0.0016</t>
   </si>
   <si>
     <t>0.9564,0.0017,0.0260,0.0006</t>
   </si>
   <si>
-    <t>0.8880,0.0061,0.0814,0.0013</t>
-  </si>
-  <si>
-    <t>0.3496,0.8121,0.0110,0.0006</t>
-  </si>
-  <si>
-    <t>0.0190,0.9570,0.3696,0.0041</t>
-  </si>
-  <si>
-    <t>0.0006,0.9278,0.9388,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0043,0.9954,0.0037</t>
-  </si>
-  <si>
-    <t>0.0359,0.0200,0.9442,0.0084</t>
-  </si>
-  <si>
-    <t>0.0840,0.0006,0.8400,0.0717</t>
-  </si>
-  <si>
-    <t>0.0010,0.9558,0.7153,0.0010</t>
+    <t>0.8881,0.0061,0.0812,0.0013</t>
+  </si>
+  <si>
+    <t>0.3489,0.8124,0.0110,0.0006</t>
+  </si>
+  <si>
+    <t>0.0190,0.9570,0.3694,0.0041</t>
+  </si>
+  <si>
+    <t>0.0006,0.9278,0.9389,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0043,0.9954,0.0037</t>
+  </si>
+  <si>
+    <t>0.0359,0.0200,0.9442,0.0085</t>
+  </si>
+  <si>
+    <t>0.0838,0.0006,0.8399,0.0719</t>
+  </si>
+  <si>
+    <t>0.0010,0.9558,0.7154,0.0010</t>
   </si>
   <si>
     <t>0.0004,0.9965,0.0062,0.0008</t>
   </si>
   <si>
-    <t>0.0051,0.0109,0.9900,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.7034,0.0013,0.9503</t>
+    <t>0.0051,0.0109,0.9899,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.7034,0.0013,0.9505</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0002,0.0001</t>
@@ -985,7 +994,7 @@
     <t>0.0159,0.0013,0.9876,0.0004</t>
   </si>
   <si>
-    <t>0.0271,0.0091,0.9663,0.0019</t>
+    <t>0.0272,0.0092,0.9663,0.0019</t>
   </si>
   <si>
     <t>0.9753,0.0130,0.0062,0.0004</t>
@@ -994,10 +1003,10 @@
     <t>0.9863,0.0012,0.0054,0.0003</t>
   </si>
   <si>
-    <t>0.9793,0.0099,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.5053,0.0007,0.5102,0.0008</t>
+    <t>0.9793,0.0099,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.5053,0.0007,0.5100,0.0008</t>
   </si>
   <si>
     <t>0.9863,0.0010,0.0057,0.0004</t>
@@ -1006,7 +1015,7 @@
     <t>0.9911,0.0021,0.0021,0.0004</t>
   </si>
   <si>
-    <t>0.9886,0.0011,0.0038,0.0002</t>
+    <t>0.9886,0.0011,0.0037,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9977,0.8977,0.0000</t>
@@ -1030,10 +1039,10 @@
     <t>0.0002,0.9994,0.0029,0.0000</t>
   </si>
   <si>
-    <t>0.9716,0.0014,0.0190,0.0002</t>
-  </si>
-  <si>
-    <t>0.2734,0.1194,0.5272,0.0026</t>
+    <t>0.9716,0.0014,0.0189,0.0002</t>
+  </si>
+  <si>
+    <t>0.2732,0.1197,0.5272,0.0027</t>
   </si>
   <si>
     <t>0.0072,0.0041,0.9904,0.0008</t>
@@ -1042,13 +1051,13 @@
     <t>0.0003,0.9707,0.9612,0.0002</t>
   </si>
   <si>
-    <t>0.0003,0.9497,0.9717,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.3143,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9655,0.9560,0.0004</t>
+    <t>0.0003,0.9498,0.9717,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.3140,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9655,0.9560,0.0003</t>
   </si>
   <si>
     <t>0.0022,0.0020,0.0013,0.9994</t>
@@ -1057,25 +1066,25 @@
     <t>0.0005,0.0010,0.0003,0.9999</t>
   </si>
   <si>
-    <t>0.0049,0.0002,0.0002,0.9994</t>
+    <t>0.0049,0.0002,0.0002,0.9995</t>
   </si>
   <si>
     <t>0.0021,0.0004,0.0011,0.9996</t>
   </si>
   <si>
-    <t>0.0062,0.0024,0.0008,0.9986</t>
+    <t>0.0061,0.0024,0.0008,0.9986</t>
   </si>
   <si>
     <t>0.0004,0.0014,0.0006,0.9998</t>
   </si>
   <si>
-    <t>0.0004,0.9974,0.4276,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.8889,0.9759,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9644,0.7845,0.0005</t>
+    <t>0.0004,0.9974,0.4277,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.8890,0.9759,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9645,0.7843,0.0005</t>
   </si>
   <si>
     <t>0.0002,0.8718,0.9892,0.0001</t>
@@ -1084,7 +1093,7 @@
     <t>0.0000,0.9930,0.9758,0.0000</t>
   </si>
   <si>
-    <t>0.0007,0.9909,0.3909,0.0003</t>
+    <t>0.0007,0.9909,0.3907,0.0003</t>
   </si>
   <si>
     <t>0.9939,0.0049,0.0004,0.0002</t>
@@ -1093,7 +1102,7 @@
     <t>0.9727,0.0180,0.0037,0.0008</t>
   </si>
   <si>
-    <t>0.9660,0.0526,0.0010,0.0002</t>
+    <t>0.9659,0.0526,0.0010,0.0002</t>
   </si>
   <si>
     <t>0.9944,0.0038,0.0006,0.0002</t>
@@ -1108,7 +1117,7 @@
     <t>0.9713,0.0047,0.0106,0.0014</t>
   </si>
   <si>
-    <t>0.9932,0.0029,0.0009,0.0004</t>
+    <t>0.9931,0.0029,0.0009,0.0004</t>
   </si>
   <si>
     <t>0.9937,0.0018,0.0009,0.0004</t>
@@ -1123,7 +1132,7 @@
     <t>0.9942,0.0025,0.0009,0.0005</t>
   </si>
   <si>
-    <t>0.9852,0.0065,0.0019,0.0016</t>
+    <t>0.9851,0.0065,0.0019,0.0017</t>
   </si>
   <si>
     <t>0.9964,0.0025,0.0003,0.0004</t>
@@ -1135,13 +1144,13 @@
     <t>0.0008,0.0001,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0576,0.0026,0.9566,0.0015</t>
+    <t>0.0575,0.0026,0.9566,0.0015</t>
   </si>
   <si>
     <t>0.9613,0.0002,0.0546,0.0000</t>
   </si>
   <si>
-    <t>0.0487,0.0011,0.9687,0.0004</t>
+    <t>0.0488,0.0011,0.9687,0.0004</t>
   </si>
   <si>
     <t>0.0002,0.9997,0.0004,0.0001</t>
@@ -1150,10 +1159,10 @@
     <t>0.0003,0.9998,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.5343,0.6262,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.1975,0.8872,0.0092,0.0011</t>
+    <t>0.5342,0.6262,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.1973,0.8874,0.0092,0.0011</t>
   </si>
   <si>
     <t>0.0004,0.9995,0.0006,0.0001</t>
@@ -1162,22 +1171,22 @@
     <t>0.0000,0.9999,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9099,0.1674,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.2494,0.0226,0.7375,0.0055</t>
-  </si>
-  <si>
-    <t>0.1084,0.0070,0.9012,0.0042</t>
-  </si>
-  <si>
-    <t>0.5540,0.0077,0.4544,0.0012</t>
+    <t>0.9096,0.1679,0.0053,0.0003</t>
+  </si>
+  <si>
+    <t>0.2494,0.0227,0.7374,0.0055</t>
+  </si>
+  <si>
+    <t>0.1085,0.0070,0.9011,0.0042</t>
+  </si>
+  <si>
+    <t>0.5542,0.0077,0.4542,0.0012</t>
   </si>
   <si>
     <t>0.2552,0.0117,0.7675,0.0053</t>
   </si>
   <si>
-    <t>0.0009,0.7696,0.7781,0.1131</t>
+    <t>0.0009,0.7695,0.7779,0.1133</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0013,0.0000</t>
@@ -1195,10 +1204,10 @@
     <t>0.0021,0.9970,0.1565,0.0003</t>
   </si>
   <si>
-    <t>0.3519,0.6573,0.0782,0.0028</t>
-  </si>
-  <si>
-    <t>0.0359,0.9593,0.0326,0.0075</t>
+    <t>0.3516,0.6575,0.0783,0.0028</t>
+  </si>
+  <si>
+    <t>0.0358,0.9594,0.0326,0.0075</t>
   </si>
   <si>
     <t>0.9963,0.0004,0.0007,0.0002</t>
@@ -1228,7 +1237,7 @@
     <t>0.0007,0.9619,0.9136,0.0003</t>
   </si>
   <si>
-    <t>0.0003,0.6205,0.9941,0.0000</t>
+    <t>0.0003,0.6208,0.9941,0.0000</t>
   </si>
   <si>
     <t>0.0006,0.0292,0.9979,0.0004</t>
@@ -1240,16 +1249,16 @@
     <t>0.9633,0.0017,0.0270,0.0002</t>
   </si>
   <si>
-    <t>0.4169,0.3257,0.1227,0.0067</t>
-  </si>
-  <si>
-    <t>0.1901,0.0004,0.8740,0.0007</t>
-  </si>
-  <si>
-    <t>0.7060,0.0075,0.2828,0.0021</t>
-  </si>
-  <si>
-    <t>0.0060,0.0001,0.0005,0.9991</t>
+    <t>0.4161,0.3265,0.1226,0.0068</t>
+  </si>
+  <si>
+    <t>0.1900,0.0004,0.8740,0.0007</t>
+  </si>
+  <si>
+    <t>0.7056,0.0075,0.2832,0.0021</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.0005,0.9991</t>
   </si>
   <si>
     <t>0.0000,0.0004,0.0005,1.0000</t>
@@ -1261,55 +1270,55 @@
     <t>0.0037,0.0003,0.0007,0.9994</t>
   </si>
   <si>
-    <t>0.0003,0.9888,0.8891,0.0001</t>
+    <t>0.0003,0.9888,0.8890,0.0001</t>
   </si>
   <si>
     <t>0.9840,0.0011,0.0063,0.0006</t>
   </si>
   <si>
-    <t>0.0355,0.9679,0.0097,0.0034</t>
+    <t>0.0354,0.9679,0.0097,0.0034</t>
   </si>
   <si>
     <t>0.9898,0.0008,0.0036,0.0003</t>
   </si>
   <si>
-    <t>0.0327,0.9773,0.0054,0.0008</t>
+    <t>0.0326,0.9774,0.0053,0.0008</t>
   </si>
   <si>
     <t>0.9913,0.0017,0.0012,0.0007</t>
   </si>
   <si>
-    <t>0.1437,0.0000,0.9334,0.0000</t>
-  </si>
-  <si>
-    <t>0.1258,0.0002,0.9157,0.0001</t>
+    <t>0.1436,0.0000,0.9335,0.0000</t>
+  </si>
+  <si>
+    <t>0.1256,0.0002,0.9158,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8745,0.0005,0.0629,0.0085</t>
-  </si>
-  <si>
-    <t>0.9639,0.0060,0.0066,0.0026</t>
-  </si>
-  <si>
-    <t>0.6311,0.2271,0.0416,0.0013</t>
+    <t>0.8741,0.0005,0.0631,0.0086</t>
+  </si>
+  <si>
+    <t>0.9638,0.0060,0.0066,0.0026</t>
+  </si>
+  <si>
+    <t>0.6306,0.2275,0.0415,0.0014</t>
   </si>
   <si>
     <t>0.9890,0.0013,0.0038,0.0002</t>
   </si>
   <si>
-    <t>0.9445,0.0355,0.0096,0.0023</t>
-  </si>
-  <si>
-    <t>0.1239,0.8840,0.0416,0.0072</t>
-  </si>
-  <si>
-    <t>0.9378,0.0097,0.0364,0.0006</t>
-  </si>
-  <si>
-    <t>0.8320,0.0247,0.1014,0.0017</t>
+    <t>0.9444,0.0355,0.0096,0.0023</t>
+  </si>
+  <si>
+    <t>0.1237,0.8843,0.0415,0.0072</t>
+  </si>
+  <si>
+    <t>0.9378,0.0097,0.0363,0.0006</t>
+  </si>
+  <si>
+    <t>0.8317,0.0247,0.1016,0.0017</t>
   </si>
   <si>
     <t>0.9943,0.0020,0.0008,0.0002</t>
@@ -1327,7 +1336,7 @@
     <t>0.9923,0.0029,0.0012,0.0002</t>
   </si>
   <si>
-    <t>0.9936,0.0026,0.0010,0.0002</t>
+    <t>0.9936,0.0026,0.0009,0.0002</t>
   </si>
   <si>
     <t>0.9898,0.0036,0.0016,0.0004</t>
@@ -1336,22 +1345,22 @@
     <t>0.9938,0.0009,0.0012,0.0003</t>
   </si>
   <si>
-    <t>0.6081,0.4981,0.0126,0.0019</t>
-  </si>
-  <si>
-    <t>0.4618,0.6603,0.0099,0.0017</t>
-  </si>
-  <si>
-    <t>0.8266,0.1890,0.0044,0.0015</t>
-  </si>
-  <si>
-    <t>0.7899,0.0420,0.1074,0.0013</t>
+    <t>0.6079,0.4981,0.0126,0.0019</t>
+  </si>
+  <si>
+    <t>0.4609,0.6610,0.0099,0.0017</t>
+  </si>
+  <si>
+    <t>0.8265,0.1889,0.0044,0.0015</t>
+  </si>
+  <si>
+    <t>0.7902,0.0420,0.1072,0.0013</t>
   </si>
   <si>
     <t>0.9924,0.0045,0.0009,0.0002</t>
   </si>
   <si>
-    <t>0.6292,0.3064,0.0429,0.0011</t>
+    <t>0.6293,0.3063,0.0428,0.0011</t>
   </si>
   <si>
     <t>0.9901,0.0019,0.0022,0.0002</t>
@@ -1363,19 +1372,19 @@
     <t>0.0069,0.0021,0.9933,0.0002</t>
   </si>
   <si>
-    <t>0.8665,0.0683,0.0391,0.0011</t>
+    <t>0.8666,0.0682,0.0390,0.0011</t>
   </si>
   <si>
     <t>0.0005,0.0005,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.4287,0.9800,0.0022</t>
-  </si>
-  <si>
-    <t>0.0149,0.0016,0.9863,0.0017</t>
-  </si>
-  <si>
-    <t>0.0019,0.6179,0.9015,0.0004</t>
+    <t>0.0002,0.4283,0.9799,0.0022</t>
+  </si>
+  <si>
+    <t>0.0149,0.0016,0.9862,0.0017</t>
+  </si>
+  <si>
+    <t>0.0019,0.6185,0.9014,0.0004</t>
   </si>
   <si>
     <t>0.0015,0.0015,0.9979,0.0001</t>
@@ -1387,67 +1396,67 @@
     <t>0.0089,0.0006,0.9938,0.0002</t>
   </si>
   <si>
-    <t>0.0984,0.0059,0.9206,0.0019</t>
-  </si>
-  <si>
-    <t>0.1624,0.0014,0.8879,0.0005</t>
-  </si>
-  <si>
-    <t>0.5052,0.1120,0.3008,0.0091</t>
+    <t>0.0986,0.0060,0.9204,0.0019</t>
+  </si>
+  <si>
+    <t>0.1626,0.0014,0.8878,0.0005</t>
+  </si>
+  <si>
+    <t>0.5049,0.1124,0.3004,0.0091</t>
   </si>
   <si>
     <t>0.0307,0.0146,0.9593,0.0027</t>
   </si>
   <si>
-    <t>0.0146,0.0211,0.9731,0.0005</t>
-  </si>
-  <si>
-    <t>0.1169,0.0043,0.9042,0.0019</t>
-  </si>
-  <si>
-    <t>0.1354,0.0034,0.8974,0.0015</t>
-  </si>
-  <si>
-    <t>0.4707,0.0241,0.5027,0.0030</t>
-  </si>
-  <si>
-    <t>0.4670,0.7590,0.0018,0.0000</t>
+    <t>0.0146,0.0212,0.9730,0.0005</t>
+  </si>
+  <si>
+    <t>0.1169,0.0043,0.9041,0.0019</t>
+  </si>
+  <si>
+    <t>0.1353,0.0034,0.8975,0.0015</t>
+  </si>
+  <si>
+    <t>0.4707,0.0242,0.5025,0.0030</t>
+  </si>
+  <si>
+    <t>0.4669,0.7590,0.0018,0.0000</t>
   </si>
   <si>
     <t>0.0080,0.9953,0.0023,0.0002</t>
   </si>
   <si>
-    <t>0.1328,0.9212,0.0074,0.0009</t>
-  </si>
-  <si>
-    <t>0.9634,0.0278,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.5792,0.5568,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.1930,0.8552,0.0111,0.0008</t>
+    <t>0.1324,0.9213,0.0074,0.0009</t>
+  </si>
+  <si>
+    <t>0.9634,0.0279,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.5787,0.5570,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.1924,0.8557,0.0111,0.0008</t>
   </si>
   <si>
     <t>0.9541,0.0161,0.0120,0.0008</t>
   </si>
   <si>
-    <t>0.4773,0.0561,0.4512,0.0191</t>
-  </si>
-  <si>
-    <t>0.2212,0.0027,0.8178,0.0038</t>
-  </si>
-  <si>
-    <t>0.3662,0.0079,0.6245,0.0029</t>
+    <t>0.4777,0.0563,0.4506,0.0191</t>
+  </si>
+  <si>
+    <t>0.2211,0.0027,0.8178,0.0039</t>
+  </si>
+  <si>
+    <t>0.3660,0.0079,0.6247,0.0029</t>
   </si>
   <si>
     <t>0.0091,0.0007,0.9926,0.0004</t>
   </si>
   <si>
-    <t>0.1247,0.0088,0.8775,0.0033</t>
-  </si>
-  <si>
-    <t>0.0759,0.0341,0.8511,0.0021</t>
+    <t>0.1245,0.0088,0.8777,0.0033</t>
+  </si>
+  <si>
+    <t>0.0759,0.0341,0.8513,0.0021</t>
   </si>
   <si>
     <t>0.0056,0.0092,0.9919,0.0011</t>
@@ -1471,22 +1480,22 @@
     <t>0.9767,0.0145,0.0031,0.0014</t>
   </si>
   <si>
-    <t>0.9788,0.0146,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.9835,0.0075,0.0022,0.0009</t>
+    <t>0.9788,0.0146,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9836,0.0075,0.0022,0.0009</t>
   </si>
   <si>
     <t>0.9894,0.0014,0.0025,0.0005</t>
   </si>
   <si>
-    <t>0.0142,0.0008,0.9904,0.0004</t>
-  </si>
-  <si>
-    <t>0.1026,0.0560,0.8569,0.0021</t>
-  </si>
-  <si>
-    <t>0.2938,0.0129,0.7106,0.0079</t>
+    <t>0.0141,0.0008,0.9904,0.0004</t>
+  </si>
+  <si>
+    <t>0.1025,0.0562,0.8569,0.0021</t>
+  </si>
+  <si>
+    <t>0.2934,0.0129,0.7109,0.0079</t>
   </si>
   <si>
     <t>0.0009,0.0005,0.9991,0.0000</t>
@@ -1495,7 +1504,7 @@
     <t>0.0003,0.0044,0.9990,0.0003</t>
   </si>
   <si>
-    <t>0.0113,0.0882,0.9596,0.0008</t>
+    <t>0.0113,0.0884,0.9595,0.0008</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9999,0.0000</t>
@@ -1507,22 +1516,22 @@
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0041,0.0118,0.9921,0.0008</t>
+    <t>0.0041,0.0118,0.9920,0.0008</t>
   </si>
   <si>
     <t>0.0356,0.0263,0.9419,0.0040</t>
   </si>
   <si>
-    <t>0.7633,0.0037,0.2400,0.0020</t>
-  </si>
-  <si>
-    <t>0.8102,0.0013,0.1839,0.0017</t>
+    <t>0.7630,0.0037,0.2403,0.0020</t>
+  </si>
+  <si>
+    <t>0.8100,0.0013,0.1840,0.0018</t>
   </si>
   <si>
     <t>0.9497,0.0085,0.0227,0.0003</t>
   </si>
   <si>
-    <t>0.9918,0.0057,0.0004,0.0002</t>
+    <t>0.9917,0.0057,0.0004,0.0002</t>
   </si>
   <si>
     <t>0.9781,0.0269,0.0011,0.0004</t>
@@ -1537,7 +1546,7 @@
     <t>0.9922,0.0021,0.0011,0.0004</t>
   </si>
   <si>
-    <t>0.9724,0.0282,0.0015,0.0005</t>
+    <t>0.9724,0.0283,0.0015,0.0005</t>
   </si>
   <si>
     <t>0.9891,0.0063,0.0016,0.0005</t>
@@ -1546,7 +1555,7 @@
     <t>0.9782,0.0082,0.0037,0.0013</t>
   </si>
   <si>
-    <t>0.0091,0.0562,0.9654,0.0011</t>
+    <t>0.0091,0.0564,0.9653,0.0011</t>
   </si>
   <si>
     <t>0.0014,0.0115,0.9974,0.0002</t>
@@ -1555,28 +1564,28 @@
     <t>0.0029,0.0039,0.9961,0.0001</t>
   </si>
   <si>
-    <t>0.0240,0.0730,0.9275,0.0010</t>
+    <t>0.0240,0.0734,0.9273,0.0010</t>
   </si>
   <si>
     <t>0.0121,0.0006,0.9924,0.0002</t>
   </si>
   <si>
-    <t>0.6979,0.0189,0.0500,0.0370</t>
-  </si>
-  <si>
-    <t>0.1716,0.0069,0.8525,0.0068</t>
+    <t>0.6969,0.0188,0.0500,0.0373</t>
+  </si>
+  <si>
+    <t>0.1718,0.0069,0.8523,0.0068</t>
   </si>
   <si>
     <t>0.0014,0.0015,0.9969,0.0017</t>
   </si>
   <si>
-    <t>0.9700,0.0004,0.0006,0.0089</t>
+    <t>0.9699,0.0004,0.0006,0.0090</t>
   </si>
   <si>
     <t>0.0006,0.0048,0.0003,0.9997</t>
   </si>
   <si>
-    <t>0.0704,0.0003,0.0005,0.9849</t>
+    <t>0.0701,0.0003,0.0005,0.9850</t>
   </si>
   <si>
     <t>0.0001,0.0003,0.0102,0.9999</t>
@@ -1585,7 +1594,7 @@
     <t>0.0002,0.0007,0.0007,0.9999</t>
   </si>
   <si>
-    <t>0.7423,0.0111,0.0073,0.1312</t>
+    <t>0.7414,0.0111,0.0073,0.1320</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1980,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1994,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2008,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,10 +2019,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2036,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2050,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2064,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2078,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2092,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2106,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2120,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2134,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2148,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,10 +2159,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,10 +2173,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,10 +2187,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2204,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2215,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,10 +2229,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2243,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,10 +2257,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2271,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,10 +2285,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,10 +2299,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,10 +2313,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,10 +2327,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,10 +2341,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,10 +2355,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2369,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2386,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2400,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,10 +2411,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,10 +2425,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2442,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2456,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,10 +2467,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2481,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2495,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2509,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2523,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,10 +2537,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2551,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2565,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2579,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,10 +2593,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2607,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2621,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2635,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2649,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2663,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2677,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,10 +2691,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,10 +2705,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,10 +2719,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2736,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2750,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2764,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,10 +2775,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2792,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2806,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2820,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2831,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2845,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2859,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2873,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2887,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2901,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2915,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2932,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,10 +2943,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,10 +2957,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2971,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2985,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2999,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3013,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3030,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3044,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3058,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3072,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3086,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3100,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3111,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3125,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3139,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3153,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3167,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3181,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3198,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3212,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3226,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3240,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3254,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3268,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3282,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3296,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3310,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3324,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3338,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3352,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3366,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3380,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3394,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3408,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3419,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,10 +3433,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3450,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,10 +3461,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3475,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3489,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3503,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3517,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3531,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3545,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3562,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,10 +3573,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,10 +3587,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3604,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,10 +3615,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3629,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3643,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3657,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3671,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3685,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3699,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3713,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,10 +3727,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3744,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3758,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3772,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3786,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3800,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3814,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3828,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3842,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3853,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3867,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3881,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3895,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3912,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3923,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,10 +3937,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3954,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3968,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3982,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3996,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4010,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4021,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4038,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4049,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4066,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,10 +4077,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4094,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,10 +4105,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4119,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4133,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4150,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4164,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4178,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4192,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4206,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,10 +4217,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4234,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4248,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4262,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4276,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4290,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4304,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4318,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4332,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4346,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4360,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4374,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,10 +4385,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4402,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4416,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4430,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4444,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4458,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4472,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,10 +4483,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4500,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4511,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4525,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,10 +4539,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4553,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4567,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4581,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,10 +4595,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,10 +4609,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,10 +4623,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4640,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,10 +4651,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,10 +4665,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,10 +4679,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,10 +4693,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,10 +4707,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,10 +4721,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,10 +4735,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,10 +4749,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4766,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,10 +4777,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,10 +4791,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4808,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,10 +4819,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,10 +4833,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,10 +4847,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,10 +4861,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,10 +4875,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,10 +4889,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4903,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4917,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4934,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4948,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4962,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4976,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4990,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5004,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5018,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5032,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,10 +5043,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,10 +5057,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,10 +5071,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5085,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5099,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,10 +5113,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5127,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,10 +5141,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5155,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5169,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,10 +5183,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5200,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5214,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5228,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5242,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5256,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5270,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5284,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5298,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5312,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5326,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5340,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5351,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5365,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5379,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,10 +5393,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,10 +5407,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5424,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,10 +5435,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5449,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5466,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5480,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5494,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5508,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5522,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5536,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
